--- a/downloads/arbeitsdateien/08_Sprachkurse_2NF_zu_3NF.xlsx
+++ b/downloads/arbeitsdateien/08_Sprachkurse_2NF_zu_3NF.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSON" sheetId="1" r:id="R458c806dd784486e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPRACHKENNTNIS" sheetId="2" r:id="Re3120dbe3726449e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PERSON" sheetId="1" r:id="Rdaa354196e3941e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SPRACHKENNTNIS" sheetId="2" r:id="R1fe2e84e948641d1"/>
   </x:sheets>
 </x:workbook>
 </file>
